--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.36540603985051</v>
+        <v>8.346878481475709</v>
       </c>
       <c r="D2" t="n">
-        <v>51.35348647280194</v>
+        <v>8.344941551830315</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8745445315524</v>
+        <v>1.767113486377265</v>
       </c>
       <c r="F2" t="n">
-        <v>10.98964625273928</v>
+        <v>1.785817516070132</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.5076291125705</v>
+        <v>4.307489730792707</v>
       </c>
       <c r="D3" t="n">
-        <v>26.13113255482077</v>
+        <v>4.246309040158375</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8745445315524</v>
+        <v>1.767113486377265</v>
       </c>
       <c r="F3" t="n">
-        <v>10.98964625273928</v>
+        <v>1.785817516070132</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.64682945575555</v>
+        <v>4.980109786560277</v>
       </c>
       <c r="D4" t="n">
-        <v>30.59675191788007</v>
+        <v>4.971972186655511</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8745445315524</v>
+        <v>1.767113486377265</v>
       </c>
       <c r="F4" t="n">
-        <v>10.98964625273928</v>
+        <v>1.785817516070132</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
